--- a/reference.xlsx
+++ b/reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\WEBSITES\AGRISTACK WEBSITE MAIN\UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B947D6F7-2A60-4B11-8FA4-33A5BA982EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B1872C-8B09-4D5B-BC98-83BDAA84CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1252,7 +1252,7 @@
         <v>286</v>
       </c>
       <c r="H2" s="3" t="str">
-        <f>IF(C2=I2,"Match","Different")</f>
+        <f t="shared" ref="H2:H33" si="0">IF(C2=I2,"Match","Different")</f>
         <v>Match</v>
       </c>
       <c r="I2" t="s">
@@ -1300,7 +1300,7 @@
         <v>769</v>
       </c>
       <c r="H3" s="3" t="str">
-        <f>IF(C3=I3,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I3" t="s">
@@ -1348,7 +1348,7 @@
         <v>1122</v>
       </c>
       <c r="H4" s="3" t="str">
-        <f>IF(C4=I4,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I4" t="s">
@@ -1396,7 +1396,7 @@
         <v>3352</v>
       </c>
       <c r="H5" s="3" t="str">
-        <f>IF(C5=I5,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I5" t="s">
@@ -1444,7 +1444,7 @@
         <v>6249</v>
       </c>
       <c r="H6" s="3" t="str">
-        <f>IF(C6=I6,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I6" t="s">
@@ -1492,7 +1492,7 @@
         <v>1684</v>
       </c>
       <c r="H7" s="3" t="str">
-        <f>IF(C7=I7,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I7" t="s">
@@ -1540,7 +1540,7 @@
         <v>4027</v>
       </c>
       <c r="H8" s="3" t="str">
-        <f>IF(C8=I8,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I8" t="s">
@@ -1588,7 +1588,7 @@
         <v>3482</v>
       </c>
       <c r="H9" s="3" t="str">
-        <f>IF(C9=I9,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I9" t="s">
@@ -1636,7 +1636,7 @@
         <v>2248</v>
       </c>
       <c r="H10" s="3" t="str">
-        <f>IF(C10=I10,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I10" t="s">
@@ -1684,7 +1684,7 @@
         <v>1194</v>
       </c>
       <c r="H11" s="3" t="str">
-        <f>IF(C11=I11,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I11" t="s">
@@ -1732,7 +1732,7 @@
         <v>1387</v>
       </c>
       <c r="H12" s="3" t="str">
-        <f>IF(C12=I12,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I12" t="s">
@@ -1780,7 +1780,7 @@
         <v>738</v>
       </c>
       <c r="H13" s="3" t="str">
-        <f>IF(C13=I13,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I13" t="s">
@@ -1828,7 +1828,7 @@
         <v>2101</v>
       </c>
       <c r="H14" s="3" t="str">
-        <f>IF(C14=I14,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I14" t="s">
@@ -1876,7 +1876,7 @@
         <v>2991</v>
       </c>
       <c r="H15" s="3" t="str">
-        <f>IF(C15=I15,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I15" t="s">
@@ -1924,7 +1924,7 @@
         <v>5007</v>
       </c>
       <c r="H16" s="3" t="str">
-        <f>IF(C16=I16,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I16" t="s">
@@ -1972,7 +1972,7 @@
         <v>429</v>
       </c>
       <c r="H17" s="3" t="str">
-        <f>IF(C17=I17,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I17" t="s">
@@ -2020,7 +2020,7 @@
         <v>594</v>
       </c>
       <c r="H18" s="3" t="str">
-        <f>IF(C18=I18,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I18" t="s">
@@ -2068,7 +2068,7 @@
         <v>5291</v>
       </c>
       <c r="H19" s="3" t="str">
-        <f>IF(C19=I19,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I19" t="s">
@@ -2116,7 +2116,7 @@
         <v>934</v>
       </c>
       <c r="H20" s="3" t="str">
-        <f>IF(C20=I20,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I20" t="s">
@@ -2164,7 +2164,7 @@
         <v>823</v>
       </c>
       <c r="H21" s="3" t="str">
-        <f>IF(C21=I21,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I21" t="s">
@@ -2212,7 +2212,7 @@
         <v>646</v>
       </c>
       <c r="H22" s="3" t="str">
-        <f>IF(C22=I22,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I22" t="s">
@@ -2260,7 +2260,7 @@
         <v>257</v>
       </c>
       <c r="H23" s="3" t="str">
-        <f>IF(C23=I23,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I23" t="s">
@@ -2308,7 +2308,7 @@
         <v>1430</v>
       </c>
       <c r="H24" s="3" t="str">
-        <f>IF(C24=I24,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I24" t="s">
@@ -2356,7 +2356,7 @@
         <v>320</v>
       </c>
       <c r="H25" s="3" t="str">
-        <f>IF(C25=I25,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I25" t="s">
@@ -2404,7 +2404,7 @@
         <v>555</v>
       </c>
       <c r="H26" s="3" t="str">
-        <f>IF(C26=I26,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I26" t="s">
@@ -2452,7 +2452,7 @@
         <v>1531</v>
       </c>
       <c r="H27" s="3" t="str">
-        <f>IF(C27=I27,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I27" t="s">
@@ -2500,7 +2500,7 @@
         <v>3500</v>
       </c>
       <c r="H28" s="3" t="str">
-        <f>IF(C28=I28,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I28" t="s">
@@ -2548,7 +2548,7 @@
         <v>1475</v>
       </c>
       <c r="H29" s="3" t="str">
-        <f>IF(C29=I29,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I29" t="s">
@@ -2596,7 +2596,7 @@
         <v>733</v>
       </c>
       <c r="H30" s="3" t="str">
-        <f>IF(C30=I30,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I30" t="s">
@@ -2644,7 +2644,7 @@
         <v>1174</v>
       </c>
       <c r="H31" s="3" t="str">
-        <f>IF(C31=I31,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I31" t="s">
@@ -2692,7 +2692,7 @@
         <v>303</v>
       </c>
       <c r="H32" s="3" t="str">
-        <f>IF(C32=I32,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I32" t="s">
@@ -2740,7 +2740,7 @@
         <v>371</v>
       </c>
       <c r="H33" s="3" t="str">
-        <f>IF(C33=I33,"Match","Different")</f>
+        <f t="shared" si="0"/>
         <v>Match</v>
       </c>
       <c r="I33" t="s">
@@ -2788,7 +2788,7 @@
         <v>719</v>
       </c>
       <c r="H34" s="3" t="str">
-        <f>IF(C34=I34,"Match","Different")</f>
+        <f t="shared" ref="H34:H65" si="1">IF(C34=I34,"Match","Different")</f>
         <v>Match</v>
       </c>
       <c r="I34" t="s">
@@ -2836,7 +2836,7 @@
         <v>2325</v>
       </c>
       <c r="H35" s="3" t="str">
-        <f>IF(C35=I35,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I35" t="s">
@@ -2884,7 +2884,7 @@
         <v>3033</v>
       </c>
       <c r="H36" s="3" t="str">
-        <f>IF(C36=I36,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I36" t="s">
@@ -2932,7 +2932,7 @@
         <v>1467</v>
       </c>
       <c r="H37" s="3" t="str">
-        <f>IF(C37=I37,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I37" t="s">
@@ -2980,7 +2980,7 @@
         <v>798</v>
       </c>
       <c r="H38" s="3" t="str">
-        <f>IF(C38=I38,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I38" t="s">
@@ -3028,7 +3028,7 @@
         <v>19</v>
       </c>
       <c r="H39" s="3" t="str">
-        <f>IF(C39=I39,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I39" t="s">
@@ -3076,7 +3076,7 @@
         <v>1285</v>
       </c>
       <c r="H40" s="3" t="str">
-        <f>IF(C40=I40,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I40" t="s">
@@ -3124,7 +3124,7 @@
         <v>847</v>
       </c>
       <c r="H41" s="3" t="str">
-        <f>IF(C41=I41,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I41" t="s">
@@ -3172,7 +3172,7 @@
         <v>700</v>
       </c>
       <c r="H42" s="3" t="str">
-        <f>IF(C42=I42,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I42" t="s">
@@ -3220,7 +3220,7 @@
         <v>224</v>
       </c>
       <c r="H43" s="3" t="str">
-        <f>IF(C43=I43,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I43" t="s">
@@ -3268,7 +3268,7 @@
         <v>658</v>
       </c>
       <c r="H44" s="3" t="str">
-        <f>IF(C44=I44,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I44" t="s">
@@ -3316,7 +3316,7 @@
         <v>801</v>
       </c>
       <c r="H45" s="3" t="str">
-        <f>IF(C45=I45,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I45" t="s">
@@ -3364,7 +3364,7 @@
         <v>1487</v>
       </c>
       <c r="H46" s="3" t="str">
-        <f>IF(C46=I46,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I46" t="s">
@@ -3412,7 +3412,7 @@
         <v>6</v>
       </c>
       <c r="H47" s="3" t="str">
-        <f>IF(C47=I47,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I47" t="s">
@@ -3460,7 +3460,7 @@
         <v>2925</v>
       </c>
       <c r="H48" s="3" t="str">
-        <f>IF(C48=I48,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I48" t="s">
@@ -3508,7 +3508,7 @@
         <v>265</v>
       </c>
       <c r="H49" s="3" t="str">
-        <f>IF(C49=I49,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I49" t="s">
@@ -3556,7 +3556,7 @@
         <v>532</v>
       </c>
       <c r="H50" s="3" t="str">
-        <f>IF(C50=I50,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I50" t="s">
@@ -3604,7 +3604,7 @@
         <v>1397</v>
       </c>
       <c r="H51" s="3" t="str">
-        <f>IF(C51=I51,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I51" t="s">
@@ -3652,7 +3652,7 @@
         <v>916</v>
       </c>
       <c r="H52" s="3" t="str">
-        <f>IF(C52=I52,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I52" t="s">
@@ -3700,7 +3700,7 @@
         <v>7460</v>
       </c>
       <c r="H53" s="3" t="str">
-        <f>IF(C53=I53,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I53" t="s">
@@ -3748,7 +3748,7 @@
         <v>2113</v>
       </c>
       <c r="H54" s="3" t="str">
-        <f>IF(C54=I54,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I54" t="s">
@@ -3796,7 +3796,7 @@
         <v>362</v>
       </c>
       <c r="H55" s="3" t="str">
-        <f>IF(C55=I55,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I55" t="s">
@@ -3844,7 +3844,7 @@
         <v>770</v>
       </c>
       <c r="H56" s="3" t="str">
-        <f>IF(C56=I56,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I56" t="s">
@@ -3892,7 +3892,7 @@
         <v>4751</v>
       </c>
       <c r="H57" s="3" t="str">
-        <f>IF(C57=I57,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I57" t="s">
@@ -3940,7 +3940,7 @@
         <v>330</v>
       </c>
       <c r="H58" s="3" t="str">
-        <f>IF(C58=I58,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I58" t="s">
@@ -3988,7 +3988,7 @@
         <v>1071</v>
       </c>
       <c r="H59" s="3" t="str">
-        <f>IF(C59=I59,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I59" t="s">
@@ -4036,7 +4036,7 @@
         <v>4056</v>
       </c>
       <c r="H60" s="3" t="str">
-        <f>IF(C60=I60,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I60" t="s">
@@ -4084,7 +4084,7 @@
         <v>718</v>
       </c>
       <c r="H61" s="3" t="str">
-        <f>IF(C61=I61,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I61" t="s">
@@ -4132,7 +4132,7 @@
         <v>526</v>
       </c>
       <c r="H62" s="3" t="str">
-        <f>IF(C62=I62,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I62" t="s">
@@ -4180,7 +4180,7 @@
         <v>1005</v>
       </c>
       <c r="H63" s="3" t="str">
-        <f>IF(C63=I63,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I63" t="s">
@@ -4228,7 +4228,7 @@
         <v>325</v>
       </c>
       <c r="H64" s="3" t="str">
-        <f>IF(C64=I64,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I64" t="s">
@@ -4276,7 +4276,7 @@
         <v>1315</v>
       </c>
       <c r="H65" s="3" t="str">
-        <f>IF(C65=I65,"Match","Different")</f>
+        <f t="shared" si="1"/>
         <v>Match</v>
       </c>
       <c r="I65" t="s">
@@ -4324,7 +4324,7 @@
         <v>227</v>
       </c>
       <c r="H66" s="3" t="str">
-        <f>IF(C66=I66,"Match","Different")</f>
+        <f t="shared" ref="H66:H97" si="2">IF(C66=I66,"Match","Different")</f>
         <v>Match</v>
       </c>
       <c r="I66" t="s">
@@ -4372,7 +4372,7 @@
         <v>2621</v>
       </c>
       <c r="H67" s="3" t="str">
-        <f>IF(C67=I67,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I67" t="s">
@@ -4420,7 +4420,7 @@
         <v>1199</v>
       </c>
       <c r="H68" s="3" t="str">
-        <f>IF(C68=I68,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I68" t="s">
@@ -4468,7 +4468,7 @@
         <v>142</v>
       </c>
       <c r="H69" s="3" t="str">
-        <f>IF(C69=I69,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I69" t="s">
@@ -4516,7 +4516,7 @@
         <v>1604</v>
       </c>
       <c r="H70" s="3" t="str">
-        <f>IF(C70=I70,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I70" t="s">
@@ -4564,7 +4564,7 @@
         <v>1221</v>
       </c>
       <c r="H71" s="3" t="str">
-        <f>IF(C71=I71,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I71" t="s">
@@ -4612,7 +4612,7 @@
         <v>776</v>
       </c>
       <c r="H72" s="3" t="str">
-        <f>IF(C72=I72,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I72" t="s">
@@ -4660,7 +4660,7 @@
         <v>747</v>
       </c>
       <c r="H73" s="3" t="str">
-        <f>IF(C73=I73,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I73" t="s">
@@ -4708,7 +4708,7 @@
         <v>3583</v>
       </c>
       <c r="H74" s="3" t="str">
-        <f>IF(C74=I74,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I74" t="s">
@@ -4756,7 +4756,7 @@
         <v>421</v>
       </c>
       <c r="H75" s="3" t="str">
-        <f>IF(C75=I75,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I75" t="s">
@@ -4804,7 +4804,7 @@
         <v>207</v>
       </c>
       <c r="H76" s="3" t="str">
-        <f>IF(C76=I76,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I76" t="s">
@@ -4852,7 +4852,7 @@
         <v>3009</v>
       </c>
       <c r="H77" s="3" t="str">
-        <f>IF(C77=I77,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I77" t="s">
@@ -4900,7 +4900,7 @@
         <v>4369</v>
       </c>
       <c r="H78" s="3" t="str">
-        <f>IF(C78=I78,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I78" t="s">
@@ -4948,7 +4948,7 @@
         <v>281</v>
       </c>
       <c r="H79" s="3" t="str">
-        <f>IF(C79=I79,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I79" t="s">
@@ -4996,7 +4996,7 @@
         <v>1535</v>
       </c>
       <c r="H80" s="3" t="str">
-        <f>IF(C80=I80,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I80" t="s">
@@ -5044,7 +5044,7 @@
         <v>565</v>
       </c>
       <c r="H81" s="3" t="str">
-        <f>IF(C81=I81,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I81" t="s">
@@ -5092,7 +5092,7 @@
         <v>1806</v>
       </c>
       <c r="H82" s="3" t="str">
-        <f>IF(C82=I82,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I82" t="s">
@@ -5140,7 +5140,7 @@
         <v>4741</v>
       </c>
       <c r="H83" s="3" t="str">
-        <f>IF(C83=I83,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I83" t="s">
@@ -5188,7 +5188,7 @@
         <v>230</v>
       </c>
       <c r="H84" s="3" t="str">
-        <f>IF(C84=I84,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I84" t="s">
@@ -5236,7 +5236,7 @@
         <v>840</v>
       </c>
       <c r="H85" s="3" t="str">
-        <f>IF(C85=I85,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I85" t="s">
@@ -5284,7 +5284,7 @@
         <v>516</v>
       </c>
       <c r="H86" s="3" t="str">
-        <f>IF(C86=I86,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I86" t="s">
@@ -5332,7 +5332,7 @@
         <v>3119</v>
       </c>
       <c r="H87" s="3" t="str">
-        <f>IF(C87=I87,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I87" t="s">
@@ -5380,7 +5380,7 @@
         <v>1110</v>
       </c>
       <c r="H88" s="3" t="str">
-        <f>IF(C88=I88,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I88" t="s">
@@ -5428,7 +5428,7 @@
         <v>1162</v>
       </c>
       <c r="H89" s="3" t="str">
-        <f>IF(C89=I89,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I89" t="s">
@@ -5476,7 +5476,7 @@
         <v>3542</v>
       </c>
       <c r="H90" s="3" t="str">
-        <f>IF(C90=I90,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I90" t="s">
@@ -5524,7 +5524,7 @@
         <v>2007</v>
       </c>
       <c r="H91" s="3" t="str">
-        <f>IF(C91=I91,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I91" t="s">
@@ -5572,7 +5572,7 @@
         <v>664</v>
       </c>
       <c r="H92" s="3" t="str">
-        <f>IF(C92=I92,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I92" t="s">
@@ -5620,7 +5620,7 @@
         <v>1539</v>
       </c>
       <c r="H93" s="3" t="str">
-        <f>IF(C93=I93,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I93" t="s">
@@ -5668,7 +5668,7 @@
         <v>166</v>
       </c>
       <c r="H94" s="3" t="str">
-        <f>IF(C94=I94,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I94" t="s">
@@ -5716,7 +5716,7 @@
         <v>5056</v>
       </c>
       <c r="H95" s="3" t="str">
-        <f>IF(C95=I95,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I95" t="s">
@@ -5764,7 +5764,7 @@
         <v>3676</v>
       </c>
       <c r="H96" s="3" t="str">
-        <f>IF(C96=I96,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I96" t="s">
@@ -5812,7 +5812,7 @@
         <v>1208</v>
       </c>
       <c r="H97" s="3" t="str">
-        <f>IF(C97=I97,"Match","Different")</f>
+        <f t="shared" si="2"/>
         <v>Match</v>
       </c>
       <c r="I97" t="s">
@@ -5860,7 +5860,7 @@
         <v>2673</v>
       </c>
       <c r="H98" s="3" t="str">
-        <f>IF(C98=I98,"Match","Different")</f>
+        <f t="shared" ref="H98:H129" si="3">IF(C98=I98,"Match","Different")</f>
         <v>Match</v>
       </c>
       <c r="I98" t="s">
@@ -5908,7 +5908,7 @@
         <v>32</v>
       </c>
       <c r="H99" s="3" t="str">
-        <f>IF(C99=I99,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I99" t="s">
@@ -5956,7 +5956,7 @@
         <v>2429</v>
       </c>
       <c r="H100" s="3" t="str">
-        <f>IF(C100=I100,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I100" t="s">
@@ -6004,7 +6004,7 @@
         <v>6463</v>
       </c>
       <c r="H101" s="3" t="str">
-        <f>IF(C101=I101,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I101" t="s">
@@ -6052,7 +6052,7 @@
         <v>387</v>
       </c>
       <c r="H102" s="3" t="str">
-        <f>IF(C102=I102,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I102" t="s">
@@ -6100,7 +6100,7 @@
         <v>3368</v>
       </c>
       <c r="H103" s="3" t="str">
-        <f>IF(C103=I103,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I103" t="s">
@@ -6148,7 +6148,7 @@
         <v>632</v>
       </c>
       <c r="H104" s="3" t="str">
-        <f>IF(C104=I104,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I104" t="s">
@@ -6193,10 +6193,10 @@
         <v>145</v>
       </c>
       <c r="G105" s="20">
-        <v>3244</v>
+        <v>3165</v>
       </c>
       <c r="H105" s="3" t="str">
-        <f>IF(C105=I105,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I105" t="s">
@@ -6244,7 +6244,7 @@
         <v>988</v>
       </c>
       <c r="H106" s="3" t="str">
-        <f>IF(C106=I106,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I106" t="s">
@@ -6292,7 +6292,7 @@
         <v>690</v>
       </c>
       <c r="H107" s="3" t="str">
-        <f>IF(C107=I107,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I107" t="s">
@@ -6340,7 +6340,7 @@
         <v>2453</v>
       </c>
       <c r="H108" s="3" t="str">
-        <f>IF(C108=I108,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I108" t="s">
@@ -6388,7 +6388,7 @@
         <v>2330</v>
       </c>
       <c r="H109" s="3" t="str">
-        <f>IF(C109=I109,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I109" t="s">
@@ -6436,7 +6436,7 @@
         <v>208</v>
       </c>
       <c r="H110" s="3" t="str">
-        <f>IF(C110=I110,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I110" t="s">
@@ -6484,7 +6484,7 @@
         <v>687</v>
       </c>
       <c r="H111" s="3" t="str">
-        <f>IF(C111=I111,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I111" t="s">
@@ -6532,7 +6532,7 @@
         <v>1057</v>
       </c>
       <c r="H112" s="3" t="str">
-        <f>IF(C112=I112,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I112" t="s">
@@ -6580,7 +6580,7 @@
         <v>1002</v>
       </c>
       <c r="H113" s="3" t="str">
-        <f>IF(C113=I113,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I113" t="s">
@@ -6628,7 +6628,7 @@
         <v>2817</v>
       </c>
       <c r="H114" s="3" t="str">
-        <f>IF(C114=I114,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I114" t="s">
@@ -6676,7 +6676,7 @@
         <v>582</v>
       </c>
       <c r="H115" s="3" t="str">
-        <f>IF(C115=I115,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I115" t="s">
@@ -6724,7 +6724,7 @@
         <v>140</v>
       </c>
       <c r="H116" s="3" t="str">
-        <f>IF(C116=I116,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I116" t="s">
@@ -6772,7 +6772,7 @@
         <v>2008</v>
       </c>
       <c r="H117" s="3" t="str">
-        <f>IF(C117=I117,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I117" t="s">
@@ -6820,7 +6820,7 @@
         <v>1657</v>
       </c>
       <c r="H118" s="3" t="str">
-        <f>IF(C118=I118,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I118" t="s">
@@ -6868,7 +6868,7 @@
         <v>926</v>
       </c>
       <c r="H119" s="3" t="str">
-        <f>IF(C119=I119,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I119" t="s">
@@ -6916,7 +6916,7 @@
         <v>2637</v>
       </c>
       <c r="H120" s="3" t="str">
-        <f>IF(C120=I120,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I120" t="s">
@@ -6964,7 +6964,7 @@
         <v>128</v>
       </c>
       <c r="H121" s="3" t="str">
-        <f>IF(C121=I121,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I121" t="s">
@@ -7012,7 +7012,7 @@
         <v>1030</v>
       </c>
       <c r="H122" s="3" t="str">
-        <f>IF(C122=I122,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I122" t="s">
@@ -7060,7 +7060,7 @@
         <v>402</v>
       </c>
       <c r="H123" s="3" t="str">
-        <f>IF(C123=I123,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I123" t="s">
@@ -7108,7 +7108,7 @@
         <v>192</v>
       </c>
       <c r="H124" s="3" t="str">
-        <f>IF(C124=I124,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I124" t="s">
@@ -7156,7 +7156,7 @@
         <v>626</v>
       </c>
       <c r="H125" s="3" t="str">
-        <f>IF(C125=I125,"Match","Different")</f>
+        <f t="shared" si="3"/>
         <v>Match</v>
       </c>
       <c r="I125" t="s">
@@ -7184,7 +7184,7 @@
     <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G126">
         <f>SUM(G2:G125)</f>
-        <v>197886</v>
+        <v>197807</v>
       </c>
     </row>
   </sheetData>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\WEBSITES\AGRISTACK WEBSITE MAIN\UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B1872C-8B09-4D5B-BC98-83BDAA84CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66842AC4-7C3A-49CC-BC55-B5FBFF76BE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5860,7 +5860,7 @@
         <v>2673</v>
       </c>
       <c r="H98" s="3" t="str">
-        <f t="shared" ref="H98:H129" si="3">IF(C98=I98,"Match","Different")</f>
+        <f t="shared" ref="H98:H125" si="3">IF(C98=I98,"Match","Different")</f>
         <v>Match</v>
       </c>
       <c r="I98" t="s">
@@ -6001,7 +6001,7 @@
         <v>145</v>
       </c>
       <c r="G101" s="20">
-        <v>6463</v>
+        <v>6388</v>
       </c>
       <c r="H101" s="3" t="str">
         <f t="shared" si="3"/>
@@ -7184,7 +7184,7 @@
     <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G126">
         <f>SUM(G2:G125)</f>
-        <v>197807</v>
+        <v>197732</v>
       </c>
     </row>
   </sheetData>
